--- a/Grid.xlsx
+++ b/Grid.xlsx
@@ -471,7 +471,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -483,7 +483,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
